--- a/report/No5_SUMMARY_テスト結果.xlsx
+++ b/report/No5_SUMMARY_テスト結果.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A559245B-173D-457C-BB6C-4CA8D8CFB553}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7648137-C7B5-4E7B-A3D3-0859EDFBBA6E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="前提" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="114">
   <si>
     <t xml:space="preserve">・SUMMARY.CBLをプリコンパイルした後にできたSUMMARY.CBOをコンパイルしてSUMMARYを作る
 </t>
@@ -959,6 +959,56 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>467173</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>152493</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="図 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5B5B53D-F3EC-45DD-A423-8F91486DA64F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="4114800"/>
+          <a:ext cx="3210373" cy="666843"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1277,6 +1327,56 @@
         </a:fontRef>
       </xdr:style>
     </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>10005</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>104956</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="図 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8ABD396C-506B-4918-A590-55776443234E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="9953625"/>
+          <a:ext cx="3439005" cy="1295581"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -4753,7 +4853,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C39875D-0247-42FE-8F51-42D6509B59AA}">
-  <dimension ref="B2:B6"/>
+  <dimension ref="B2:B24"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
@@ -4774,6 +4874,11 @@
     <row r="6" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B6" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B24" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -4785,7 +4890,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E554D5A-483A-4E96-9F93-F9234EB1B911}">
-  <dimension ref="B2:O24"/>
+  <dimension ref="B2:O58"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.15">
@@ -4898,10 +5003,16 @@
         <v>31</v>
       </c>
     </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B58" t="s">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
